--- a/research/traditional_assets/database/data/mexico/mexico_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_banks_regional.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09369999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="E2">
-        <v>0.07519999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="F2">
-        <v>0.151</v>
+        <v>0.197</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>153.4</v>
+        <v>225.7</v>
       </c>
       <c r="L2">
-        <v>0.3437149899170961</v>
+        <v>0.4043353636689358</v>
       </c>
       <c r="M2">
-        <v>87.8772</v>
+        <v>201.41</v>
       </c>
       <c r="N2">
-        <v>0.05173812187224022</v>
+        <v>0.08551715353260871</v>
       </c>
       <c r="O2">
-        <v>0.5728631029986962</v>
+        <v>0.8923792645104121</v>
       </c>
       <c r="P2">
-        <v>87.8772</v>
+        <v>198</v>
       </c>
       <c r="Q2">
-        <v>0.05173812187224022</v>
+        <v>0.08406929347826088</v>
       </c>
       <c r="R2">
-        <v>0.5728631029986962</v>
+        <v>0.8772707133362871</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.409999999999997</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01693063899508464</v>
       </c>
       <c r="U2">
-        <v>380.1</v>
+        <v>502.1</v>
       </c>
       <c r="V2">
-        <v>0.2237856932587577</v>
+        <v>0.2131878396739131</v>
       </c>
       <c r="W2">
-        <v>0.155278874379998</v>
+        <v>0.1967913505972622</v>
       </c>
       <c r="X2">
-        <v>0.1524573177640703</v>
+        <v>0.1529707327844843</v>
       </c>
       <c r="Y2">
-        <v>0.002821556615927673</v>
+        <v>0.04382061781277782</v>
       </c>
       <c r="Z2">
-        <v>0.07328888596952182</v>
+        <v>0.07652760450226896</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05455985515056322</v>
+        <v>0.07257262698641496</v>
       </c>
       <c r="AC2">
-        <v>-0.05455985515056322</v>
+        <v>-0.07257262698641496</v>
       </c>
       <c r="AD2">
-        <v>6527.3</v>
+        <v>8177.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6527.3</v>
+        <v>8177.7</v>
       </c>
       <c r="AG2">
-        <v>6147.2</v>
+        <v>7675.599999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7935155243259016</v>
+        <v>0.7763958643868261</v>
       </c>
       <c r="AI2">
-        <v>0.8505511975189596</v>
+        <v>0.8728932059561295</v>
       </c>
       <c r="AJ2">
-        <v>0.783511987458098</v>
+        <v>0.7652031742233919</v>
       </c>
       <c r="AK2">
-        <v>0.8427633292661191</v>
+        <v>0.8656952088784625</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09369999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="E3">
-        <v>0.07519999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="F3">
-        <v>0.151</v>
+        <v>0.197</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>153.4</v>
+        <v>225.7</v>
       </c>
       <c r="L3">
-        <v>0.3437149899170961</v>
+        <v>0.4043353636689358</v>
       </c>
       <c r="M3">
-        <v>87.8772</v>
+        <v>201.41</v>
       </c>
       <c r="N3">
-        <v>0.05173812187224022</v>
+        <v>0.08551715353260871</v>
       </c>
       <c r="O3">
-        <v>0.5728631029986962</v>
+        <v>0.8923792645104121</v>
       </c>
       <c r="P3">
-        <v>87.8772</v>
+        <v>198</v>
       </c>
       <c r="Q3">
-        <v>0.05173812187224022</v>
+        <v>0.08406929347826088</v>
       </c>
       <c r="R3">
-        <v>0.5728631029986962</v>
+        <v>0.8772707133362871</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.409999999999997</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01693063899508464</v>
       </c>
       <c r="U3">
-        <v>380.1</v>
+        <v>502.1</v>
       </c>
       <c r="V3">
-        <v>0.2237856932587577</v>
+        <v>0.2131878396739131</v>
       </c>
       <c r="W3">
-        <v>0.155278874379998</v>
+        <v>0.1967913505972622</v>
       </c>
       <c r="X3">
-        <v>0.1524573177640703</v>
+        <v>0.1529707327844843</v>
       </c>
       <c r="Y3">
-        <v>0.002821556615927673</v>
+        <v>0.04382061781277782</v>
       </c>
       <c r="Z3">
-        <v>0.07328888596952182</v>
+        <v>0.07652760450226896</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05455985515056322</v>
+        <v>0.07257262698641496</v>
       </c>
       <c r="AC3">
-        <v>-0.05455985515056322</v>
+        <v>-0.07257262698641496</v>
       </c>
       <c r="AD3">
-        <v>6527.3</v>
+        <v>8177.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6527.3</v>
+        <v>8177.7</v>
       </c>
       <c r="AG3">
-        <v>6147.2</v>
+        <v>7675.599999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7935155243259016</v>
+        <v>0.7763958643868261</v>
       </c>
       <c r="AI3">
-        <v>0.8505511975189596</v>
+        <v>0.8728932059561295</v>
       </c>
       <c r="AJ3">
-        <v>0.783511987458098</v>
+        <v>0.7652031742233919</v>
       </c>
       <c r="AK3">
-        <v>0.8427633292661191</v>
+        <v>0.8656952088784625</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/mexico/mexico_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_banks_regional.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.098</v>
+        <v>0.164</v>
       </c>
       <c r="E2">
-        <v>0.109</v>
+        <v>0.179</v>
       </c>
       <c r="F2">
-        <v>0.197</v>
+        <v>0.133</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>225.7</v>
+        <v>309.4</v>
       </c>
       <c r="L2">
-        <v>0.4043353636689358</v>
+        <v>0.4128636242327195</v>
       </c>
       <c r="M2">
-        <v>201.41</v>
+        <v>142.9644</v>
       </c>
       <c r="N2">
-        <v>0.08551715353260871</v>
+        <v>0.04542012962256958</v>
       </c>
       <c r="O2">
-        <v>0.8923792645104121</v>
+        <v>0.4620698125404007</v>
       </c>
       <c r="P2">
-        <v>198</v>
+        <v>142.9644</v>
       </c>
       <c r="Q2">
-        <v>0.08406929347826088</v>
+        <v>0.04542012962256958</v>
       </c>
       <c r="R2">
-        <v>0.8772707133362871</v>
+        <v>0.4620698125404007</v>
       </c>
       <c r="S2">
-        <v>3.409999999999997</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01693063899508464</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>502.1</v>
+        <v>539.6</v>
       </c>
       <c r="V2">
-        <v>0.2131878396739131</v>
+        <v>0.1714322023128733</v>
       </c>
       <c r="W2">
-        <v>0.1967913505972622</v>
+        <v>0.259825327510917</v>
       </c>
       <c r="X2">
-        <v>0.1529707327844843</v>
+        <v>0.07346696137528147</v>
       </c>
       <c r="Y2">
-        <v>0.04382061781277782</v>
+        <v>0.1863583661356356</v>
       </c>
       <c r="Z2">
-        <v>0.07652760450226896</v>
+        <v>0.08453935976156605</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07257262698641496</v>
+        <v>0.06076843865806614</v>
       </c>
       <c r="AC2">
-        <v>-0.07257262698641496</v>
+        <v>-0.06076843865806614</v>
       </c>
       <c r="AD2">
-        <v>8177.7</v>
+        <v>2715.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8177.7</v>
+        <v>2715.7</v>
       </c>
       <c r="AG2">
-        <v>7675.599999999999</v>
+        <v>2176.1</v>
       </c>
       <c r="AH2">
-        <v>0.7763958643868261</v>
+        <v>0.4631692050551737</v>
       </c>
       <c r="AI2">
-        <v>0.8728932059561295</v>
+        <v>0.6280817799158148</v>
       </c>
       <c r="AJ2">
-        <v>0.7652031742233919</v>
+        <v>0.4087570674530872</v>
       </c>
       <c r="AK2">
-        <v>0.8656952088784625</v>
+        <v>0.5750488874795201</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.098</v>
+        <v>0.164</v>
       </c>
       <c r="E3">
-        <v>0.109</v>
+        <v>0.179</v>
       </c>
       <c r="F3">
-        <v>0.197</v>
+        <v>0.133</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>225.7</v>
+        <v>309.4</v>
       </c>
       <c r="L3">
-        <v>0.4043353636689358</v>
+        <v>0.4128636242327195</v>
       </c>
       <c r="M3">
-        <v>201.41</v>
+        <v>142.9644</v>
       </c>
       <c r="N3">
-        <v>0.08551715353260871</v>
+        <v>0.04542012962256958</v>
       </c>
       <c r="O3">
-        <v>0.8923792645104121</v>
+        <v>0.4620698125404007</v>
       </c>
       <c r="P3">
-        <v>198</v>
+        <v>142.9644</v>
       </c>
       <c r="Q3">
-        <v>0.08406929347826088</v>
+        <v>0.04542012962256958</v>
       </c>
       <c r="R3">
-        <v>0.8772707133362871</v>
+        <v>0.4620698125404007</v>
       </c>
       <c r="S3">
-        <v>3.409999999999997</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01693063899508464</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>502.1</v>
+        <v>539.6</v>
       </c>
       <c r="V3">
-        <v>0.2131878396739131</v>
+        <v>0.1714322023128733</v>
       </c>
       <c r="W3">
-        <v>0.1967913505972622</v>
+        <v>0.259825327510917</v>
       </c>
       <c r="X3">
-        <v>0.1529707327844843</v>
+        <v>0.07346696137528147</v>
       </c>
       <c r="Y3">
-        <v>0.04382061781277782</v>
+        <v>0.1863583661356356</v>
       </c>
       <c r="Z3">
-        <v>0.07652760450226896</v>
+        <v>0.08453935976156605</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07257262698641496</v>
+        <v>0.06076843865806614</v>
       </c>
       <c r="AC3">
-        <v>-0.07257262698641496</v>
+        <v>-0.06076843865806614</v>
       </c>
       <c r="AD3">
-        <v>8177.7</v>
+        <v>2715.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8177.7</v>
+        <v>2715.7</v>
       </c>
       <c r="AG3">
-        <v>7675.599999999999</v>
+        <v>2176.1</v>
       </c>
       <c r="AH3">
-        <v>0.7763958643868261</v>
+        <v>0.4631692050551737</v>
       </c>
       <c r="AI3">
-        <v>0.8728932059561295</v>
+        <v>0.6280817799158148</v>
       </c>
       <c r="AJ3">
-        <v>0.7652031742233919</v>
+        <v>0.4087570674530872</v>
       </c>
       <c r="AK3">
-        <v>0.8656952088784625</v>
+        <v>0.5750488874795201</v>
       </c>
       <c r="AL3">
         <v>0</v>
